--- a/cet4/result/47_重生商女_豪门弃女的逆袭/47_重生商女_豪门弃女的逆袭_学习版.xlsx
+++ b/cet4/result/47_重生商女_豪门弃女的逆袭/47_重生商女_豪门弃女的逆袭_学习版.xlsx
@@ -399,724 +399,724 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>telescope</v>
       </c>
       <c r="B2" t="str">
-        <v>telescope</v>
+        <v>/ˈtelɪskoʊp/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D2" t="str">
         <v>望远镜</v>
       </c>
-      <c r="D2" t="str">
-        <v>telescope(望远镜)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>betray</v>
       </c>
       <c r="B3" t="str">
-        <v>betray</v>
+        <v>/bɪˈtreɪ/</v>
       </c>
       <c r="C3" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D3" t="str">
         <v>背叛</v>
       </c>
-      <c r="D3" t="str">
-        <v>betray(背叛)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>friend</v>
       </c>
       <c r="B4" t="str">
-        <v>friend</v>
+        <v>/frend/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>朋友</v>
       </c>
-      <c r="D4" t="str">
-        <v>friend(朋友)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>possession</v>
       </c>
       <c r="B5" t="str">
-        <v>possession</v>
+        <v>/pəˈzeʃn/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>财产</v>
       </c>
-      <c r="D5" t="str">
-        <v>possession(财产)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>sob</v>
       </c>
       <c r="B6" t="str">
-        <v>sob</v>
+        <v>/sɑːb/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>啜泣</v>
       </c>
-      <c r="D6" t="str">
-        <v>sob(啜泣)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>not</v>
       </c>
       <c r="B7" t="str">
-        <v>not</v>
+        <v>/nɑːt/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./v./adv.</v>
+      </c>
+      <c r="D7" t="str">
         <v>不</v>
       </c>
-      <c r="D7" t="str">
-        <v>not(不)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>after</v>
       </c>
       <c r="B8" t="str">
-        <v>after</v>
+        <v>/ˈæftər/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./adj./adv./prep./conj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>在...之后</v>
       </c>
-      <c r="D8" t="str">
-        <v>after(在...之后)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>lively</v>
       </c>
       <c r="B9" t="str">
-        <v>lively</v>
+        <v>/ˈlaɪvli/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>活泼的</v>
       </c>
-      <c r="D9" t="str">
-        <v>lively(活泼的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>German</v>
       </c>
       <c r="B10" t="str">
-        <v>German</v>
+        <v>/ˈdʒɜːrmən/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>德国的</v>
       </c>
-      <c r="D10" t="str">
-        <v>German(德国的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>stair</v>
       </c>
       <c r="B11" t="str">
-        <v>stair</v>
+        <v>/ster/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>楼梯</v>
       </c>
-      <c r="D11" t="str">
-        <v>stair(楼梯)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>fairly</v>
       </c>
       <c r="B12" t="str">
-        <v>fairly</v>
+        <v>/ˈferli/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./v./adv.</v>
+      </c>
+      <c r="D12" t="str">
         <v>相当地</v>
       </c>
-      <c r="D12" t="str">
-        <v>fairly(相当地)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>emotion</v>
       </c>
       <c r="B13" t="str">
-        <v>emotion</v>
+        <v>/ɪˈmoʊʃn/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>情感</v>
       </c>
-      <c r="D13" t="str">
-        <v>emotion(情感)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>overall</v>
       </c>
       <c r="B14" t="str">
-        <v>overall</v>
+        <v>/ˌoʊvərˈɔːl; ˈoʊvərɔːl/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D14" t="str">
         <v>全部的</v>
       </c>
-      <c r="D14" t="str">
-        <v>overall(全部的)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>analysis</v>
       </c>
       <c r="B15" t="str">
-        <v>analysis</v>
+        <v>/əˈnæləsɪs/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>分析</v>
       </c>
-      <c r="D15" t="str">
-        <v>analysis(分析)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>calculator</v>
       </c>
       <c r="B16" t="str">
-        <v>calculator</v>
+        <v>/ˈkælkjuleɪtər/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>计算器</v>
       </c>
-      <c r="D16" t="str">
-        <v>calculator(计算器)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>always</v>
       </c>
       <c r="B17" t="str">
-        <v>always</v>
+        <v>/ˈɔːlweɪz/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D17" t="str">
         <v>永远</v>
       </c>
-      <c r="D17" t="str">
-        <v>always(永远)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>tenant</v>
       </c>
       <c r="B18" t="str">
-        <v>tenant</v>
+        <v>/ˈtenənt/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>租户</v>
       </c>
-      <c r="D18" t="str">
-        <v>tenant(租户)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>vertical</v>
       </c>
       <c r="B19" t="str">
-        <v>vertical</v>
+        <v>/ˈvɜːrtɪkl/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>垂直的</v>
       </c>
-      <c r="D19" t="str">
-        <v>vertical(垂直的)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>upstairs</v>
       </c>
       <c r="B20" t="str">
-        <v>upstairs</v>
+        <v>/ˌʌpˈsterz/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D20" t="str">
         <v>楼上</v>
       </c>
-      <c r="D20" t="str">
-        <v>upstairs(楼上)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>backward</v>
       </c>
       <c r="B21" t="str">
-        <v>backward</v>
+        <v>/ˈbækwərd/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D21" t="str">
         <v>向后</v>
       </c>
-      <c r="D21" t="str">
-        <v>backward(向后)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>fund</v>
       </c>
       <c r="B22" t="str">
-        <v>fund</v>
+        <v>/fʌnd/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D22" t="str">
         <v>基金</v>
       </c>
-      <c r="D22" t="str">
-        <v>fund(基金)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>devise</v>
       </c>
       <c r="B23" t="str">
-        <v>devise</v>
+        <v>/dɪˈvaɪz/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D23" t="str">
         <v>设计</v>
       </c>
-      <c r="D23" t="str">
-        <v>devise(设计)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>daring</v>
       </c>
       <c r="B24" t="str">
-        <v>daring</v>
+        <v>/ˈderɪŋ/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>大胆的</v>
       </c>
-      <c r="D24" t="str">
-        <v>daring(大胆的)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>maintenance</v>
       </c>
       <c r="B25" t="str">
-        <v>maintenance</v>
+        <v>/ˈmeɪntənəns/</v>
       </c>
       <c r="C25" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>维护</v>
       </c>
-      <c r="D25" t="str">
-        <v>maintenance(维护)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>actress</v>
       </c>
       <c r="B26" t="str">
-        <v>actress</v>
+        <v>/ˈæktrəs/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>女演员</v>
       </c>
-      <c r="D26" t="str">
-        <v>actress(女演员)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>overtime</v>
       </c>
       <c r="B27" t="str">
-        <v>overtime</v>
+        <v>/ˈoʊvərtaɪm/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./vt./v./adj./adv.</v>
+      </c>
+      <c r="D27" t="str">
         <v>加班</v>
       </c>
-      <c r="D27" t="str">
-        <v>overtime(加班)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>health</v>
       </c>
       <c r="B28" t="str">
-        <v>health</v>
+        <v>/helθ/</v>
       </c>
       <c r="C28" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>健康</v>
       </c>
-      <c r="D28" t="str">
-        <v>health(健康)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>mud</v>
       </c>
       <c r="B29" t="str">
-        <v>mud</v>
+        <v>/mʌd/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D29" t="str">
         <v>泥</v>
       </c>
-      <c r="D29" t="str">
-        <v>mud(泥)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>barn</v>
       </c>
       <c r="B30" t="str">
-        <v>barn</v>
+        <v>/bɑːrn/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D30" t="str">
         <v>谷仓</v>
       </c>
-      <c r="D30" t="str">
-        <v>barn(谷仓)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>telephone</v>
       </c>
       <c r="B31" t="str">
-        <v>telephone</v>
+        <v>/ˈtelɪfoʊn/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D31" t="str">
         <v>电话</v>
       </c>
-      <c r="D31" t="str">
-        <v>telephone(电话)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>form</v>
       </c>
       <c r="B32" t="str">
-        <v>form</v>
+        <v>/fɔːrm/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D32" t="str">
         <v>形式</v>
       </c>
-      <c r="D32" t="str">
-        <v>form(形式)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>museum</v>
       </c>
       <c r="B33" t="str">
-        <v>museum</v>
+        <v>/mjuˈziːəm/</v>
       </c>
       <c r="C33" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>博物馆</v>
       </c>
-      <c r="D33" t="str">
-        <v>museum(博物馆)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>metal</v>
       </c>
       <c r="B34" t="str">
-        <v>metal</v>
+        <v>/ˈmetl/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D34" t="str">
         <v>金属</v>
       </c>
-      <c r="D34" t="str">
-        <v>metal(金属)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>hen</v>
       </c>
       <c r="B35" t="str">
-        <v>hen</v>
+        <v>/hen/</v>
       </c>
       <c r="C35" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>母鸡</v>
       </c>
-      <c r="D35" t="str">
-        <v>hen(母鸡)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>corresponding</v>
       </c>
       <c r="B36" t="str">
-        <v>corresponding</v>
+        <v>/ˌkɔːrəˈspɑːndɪŋ/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./adj.</v>
+      </c>
+      <c r="D36" t="str">
         <v>相应的</v>
       </c>
-      <c r="D36" t="str">
-        <v>corresponding(相应的)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>hit</v>
       </c>
       <c r="B37" t="str">
-        <v>hit</v>
+        <v>/hɪt/</v>
       </c>
       <c r="C37" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D37" t="str">
         <v>打击</v>
       </c>
-      <c r="D37" t="str">
-        <v>hit(打击)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>compromise</v>
       </c>
       <c r="B38" t="str">
-        <v>compromise</v>
+        <v>/ˈkɑːmprəmaɪz/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D38" t="str">
         <v>妥协</v>
       </c>
-      <c r="D38" t="str">
-        <v>compromise(妥协)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>feeling</v>
       </c>
       <c r="B39" t="str">
-        <v>feeling</v>
+        <v>/ˈfiːlɪŋ/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D39" t="str">
         <v>感觉</v>
       </c>
-      <c r="D39" t="str">
-        <v>feeling(感觉)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>prime</v>
       </c>
       <c r="B40" t="str">
-        <v>prime</v>
+        <v>/praɪm/</v>
       </c>
       <c r="C40" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D40" t="str">
         <v>最好的</v>
       </c>
-      <c r="D40" t="str">
-        <v>prime(最好的)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>military</v>
       </c>
       <c r="B41" t="str">
-        <v>military</v>
+        <v>/ˈmɪləteri/</v>
       </c>
       <c r="C41" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D41" t="str">
         <v>军事</v>
       </c>
-      <c r="D41" t="str">
-        <v>military(军事)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>liberal</v>
       </c>
       <c r="B42" t="str">
-        <v>liberal</v>
+        <v>/ˈlɪbərəl/</v>
       </c>
       <c r="C42" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D42" t="str">
         <v>自由主义的</v>
       </c>
-      <c r="D42" t="str">
-        <v>liberal(自由主义的)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>kindness</v>
       </c>
       <c r="B43" t="str">
-        <v>kindness</v>
+        <v>/ˈkaɪndnəs/</v>
       </c>
       <c r="C43" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>仁慈</v>
       </c>
-      <c r="D43" t="str">
-        <v>kindness(仁慈)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>protein</v>
       </c>
       <c r="B44" t="str">
-        <v>protein</v>
+        <v>/ˈproʊtiːn/</v>
       </c>
       <c r="C44" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D44" t="str">
         <v>蛋白质</v>
       </c>
-      <c r="D44" t="str">
-        <v>protein(蛋白质)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>tool</v>
       </c>
       <c r="B45" t="str">
-        <v>tool</v>
+        <v>/tuːl/</v>
       </c>
       <c r="C45" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D45" t="str">
         <v>工具</v>
       </c>
-      <c r="D45" t="str">
-        <v>tool(工具)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>jungle</v>
       </c>
       <c r="B46" t="str">
-        <v>jungle</v>
+        <v>/ˈdʒʌŋɡl/</v>
       </c>
       <c r="C46" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D46" t="str">
         <v>丛林</v>
       </c>
-      <c r="D46" t="str">
-        <v>jungle(丛林)📢</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>subtract</v>
       </c>
       <c r="B47" t="str">
-        <v>subtract</v>
+        <v>/səbˈtrækt/</v>
       </c>
       <c r="C47" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D47" t="str">
         <v>减去</v>
       </c>
-      <c r="D47" t="str">
-        <v>subtract(减去)📢</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>rod</v>
       </c>
       <c r="B48" t="str">
-        <v>rod</v>
+        <v>/rɑːd/</v>
       </c>
       <c r="C48" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>棒</v>
       </c>
-      <c r="D48" t="str">
-        <v>rod(棒)📢</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>treatment</v>
       </c>
       <c r="B49" t="str">
-        <v>treatment</v>
+        <v>/ˈtriːtmənt/</v>
       </c>
       <c r="C49" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D49" t="str">
         <v>治疗</v>
       </c>
-      <c r="D49" t="str">
-        <v>treatment(治疗)📢</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>pity</v>
       </c>
       <c r="B50" t="str">
-        <v>pity</v>
+        <v>/ˈpɪti/</v>
       </c>
       <c r="C50" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D50" t="str">
         <v>怜悯</v>
       </c>
-      <c r="D50" t="str">
-        <v>pity(怜悯)📢</v>
-      </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>strip</v>
       </c>
       <c r="B51" t="str">
-        <v>strip</v>
+        <v>/strɪp/</v>
       </c>
       <c r="C51" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D51" t="str">
         <v>剥去</v>
-      </c>
-      <c r="D51" t="str">
-        <v>strip(剥去)📢</v>
       </c>
     </row>
   </sheetData>
